--- a/artfynd/A 16684-2023 artfynd.xlsx
+++ b/artfynd/A 16684-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 16684-2023 artfynd.xlsx
+++ b/artfynd/A 16684-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90237070</v>
+        <v>90237059</v>
       </c>
       <c r="B2" t="n">
-        <v>60384</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>61744</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,7 +703,11 @@
           <t>(Dupuy, 1849)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>ex.</t>
@@ -726,14 +725,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Börringesjön, N Lindeved 1, Sk</t>
+          <t>Börringesjön, N Lindeved 3, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>393240.51804228</v>
+        <v>393455</v>
       </c>
       <c r="R2" t="n">
-        <v>6152025.638149635</v>
+        <v>6152097</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -765,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -775,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +788,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Halvöppet område i alsumpskog med högstarr och nässlor. Torrt vid inventeringstillfället.</t>
+          <t>Halvöppet i alsumpskog med högstarr och nässlor. Torr vegetation.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -804,6 +803,146 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Större grynsnäcka</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>90237065</v>
+      </c>
+      <c r="B3" t="n">
+        <v>61744</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>101968</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Större grynsnäcka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Vertigo moulinsiana</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Dupuy, 1849)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>juvenil</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>bankning</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Börringesjön, N Lindeved 2, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>393453</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6152099</v>
+      </c>
+      <c r="S3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Svedala</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Börringe</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2020-09-10</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2020-09-10</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Öppet med torr hög vegetation.</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Olle Jonsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Olle Jonsson, Monika Sunhede</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Större grynsnäcka</t>
         </is>

--- a/artfynd/A 16684-2023 artfynd.xlsx
+++ b/artfynd/A 16684-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -807,6 +812,11 @@
           <t>Större grynsnäcka</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90237059</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -947,8 +957,17 @@
           <t>Större grynsnäcka</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90237065</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>